--- a/data/2026-06-26_dados-brutos_movimentacao-estoque.xlsx
+++ b/data/2026-06-26_dados-brutos_movimentacao-estoque.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/92f769f869d4c6fb/1 Projects/PROJ011_Airflow-pipeline-test/Nível 1 - Simples/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_E85C78AF514FCA0F621720D44239A6B80B0FA35F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83B44D35-7635-45DD-AD31-FA4592BB5C7F}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_E85C78AF514FCA0F621720D44239A6B80B0FA35F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7452C78-6905-4A16-BDA0-F80012F98D45}"/>
   <bookViews>
-    <workbookView xWindow="7755" yWindow="360" windowWidth="13275" windowHeight="15825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3600" yWindow="2310" windowWidth="21600" windowHeight="11565" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="movimentacao" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="47">
   <si>
     <t>id_movimentacao</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t>l03</t>
+  </si>
+  <si>
+    <t>L04</t>
   </si>
 </sst>
 </file>
@@ -504,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1015,6 +1018,29 @@
         <v>50</v>
       </c>
     </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
